--- a/outputs/05_benchmark_signals/tables_v_viii/cn/table_vii_return_logit.xlsx
+++ b/outputs/05_benchmark_signals/tables_v_viii/cn/table_vii_return_logit.xlsx
@@ -472,35 +472,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.00*** (3.3)</t>
+          <t>3.85*** (6.8)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.00** (2.4)</t>
+          <t>1.01** (2.4)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.00*** (3.5)</t>
+          <t>2.45*** (5.1)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.00 (0.9)</t>
+          <t>0.16 (1.3)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.00*** (3.7)</t>
+          <t>1.85*** (4.8)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.00 (0.7)</t>
+          <t>0.07 (0.9)</t>
         </is>
       </c>
     </row>
@@ -513,34 +513,34 @@
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.00** (-2.4)</t>
+          <t>-0.34** (-2.2)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-0.00** (-2.4)</t>
+          <t>-0.35** (-2.2)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-0.00** (-2.4)</t>
+          <t>-0.34** (-2.2)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-0.00** (-2.4)</t>
+          <t>-0.34** (-2.2)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.00** (-2.4)</t>
+          <t>-0.34** (-2.2)</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-0.00** (-2.4)</t>
+          <t>-0.34** (-2.2)</t>
         </is>
       </c>
     </row>
@@ -553,34 +553,34 @@
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.00*** (3.0)</t>
+          <t>0.67*** (3.8)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.00*** (2.9)</t>
+          <t>0.67*** (3.7)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.00*** (3.0)</t>
+          <t>0.67*** (3.8)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.00*** (2.9)</t>
+          <t>0.65*** (3.7)</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.00*** (3.0)</t>
+          <t>0.67*** (3.8)</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.00*** (3.0)</t>
+          <t>0.67*** (3.8)</t>
         </is>
       </c>
     </row>
@@ -593,34 +593,34 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.00*** (2.8)</t>
+          <t>0.50*** (2.7)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.00*** (2.7)</t>
+          <t>0.32* (1.7)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.00*** (2.8)</t>
+          <t>0.50*** (2.7)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.00*** (2.8)</t>
+          <t>0.47** (2.5)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.00*** (2.8)</t>
+          <t>0.50*** (2.7)</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.00*** (2.9)</t>
+          <t>0.50*** (2.7)</t>
         </is>
       </c>
     </row>
@@ -633,34 +633,34 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.00 (0.8)</t>
+          <t>0.08 (0.6)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.00 (0.8)</t>
+          <t>0.07 (0.6)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.00 (0.8)</t>
+          <t>0.08 (0.6)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.00 (0.7)</t>
+          <t>0.06 (0.5)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.00 (0.8)</t>
+          <t>0.08 (0.6)</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.00 (0.6)</t>
+          <t>0.06 (0.5)</t>
         </is>
       </c>
     </row>
@@ -673,34 +673,34 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.00* (1.9)</t>
+          <t>0.18* (1.7)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.00* (1.8)</t>
+          <t>0.17 (1.6)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.00* (1.9)</t>
+          <t>0.18* (1.7)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.00* (1.9)</t>
+          <t>0.18* (1.7)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.00* (1.9)</t>
+          <t>0.18* (1.7)</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.00* (1.9)</t>
+          <t>0.18* (1.7)</t>
         </is>
       </c>
     </row>
@@ -713,34 +713,34 @@
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.00*** (-3.1)</t>
+          <t>-0.33*** (-3.3)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-0.00*** (-3.1)</t>
+          <t>-0.34*** (-3.3)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-0.00*** (-3.1)</t>
+          <t>-0.33*** (-3.3)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-0.00*** (-2.9)</t>
+          <t>-0.33*** (-3.2)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.00*** (-3.1)</t>
+          <t>-0.33*** (-3.3)</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-0.00*** (-2.9)</t>
+          <t>-0.33*** (-3.2)</t>
         </is>
       </c>
     </row>
@@ -753,34 +753,34 @@
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.00 (-1.2)</t>
+          <t>-0.12 (-1.2)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-0.00 (-1.2)</t>
+          <t>-0.12 (-1.3)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-0.00 (-1.2)</t>
+          <t>-0.12 (-1.2)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-0.00 (-1.2)</t>
+          <t>-0.12 (-1.2)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.00 (-1.2)</t>
+          <t>-0.12 (-1.2)</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-0.00 (-1.2)</t>
+          <t>-0.12 (-1.3)</t>
         </is>
       </c>
     </row>
@@ -793,34 +793,34 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.00*** (-3.8)</t>
+          <t>-0.87*** (-4.0)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-0.00*** (-3.7)</t>
+          <t>-0.86*** (-3.9)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-0.00*** (-3.8)</t>
+          <t>-0.87*** (-4.0)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-0.00*** (-3.8)</t>
+          <t>-0.88*** (-4.0)</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.00*** (-3.8)</t>
+          <t>-0.87*** (-4.0)</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-0.00*** (-3.8)</t>
+          <t>-0.89*** (-4.0)</t>
         </is>
       </c>
     </row>
@@ -833,34 +833,34 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.00*** (2.9)</t>
+          <t>0.40*** (2.8)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.00*** (2.8)</t>
+          <t>0.25* (1.6)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.00*** (2.9)</t>
+          <t>0.40*** (2.8)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.00*** (2.9)</t>
+          <t>0.38** (2.6)</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.00*** (2.9)</t>
+          <t>0.40*** (2.8)</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.00*** (3.0)</t>
+          <t>0.40*** (2.8)</t>
         </is>
       </c>
     </row>
@@ -873,34 +873,34 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.00** (-2.1)</t>
+          <t>-0.33** (-2.3)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-0.00** (-2.1)</t>
+          <t>-0.34** (-2.4)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-0.00** (-2.1)</t>
+          <t>-0.33** (-2.3)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-0.00** (-2.0)</t>
+          <t>-0.32** (-2.2)</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.00** (-2.1)</t>
+          <t>-0.33** (-2.3)</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-0.00** (-2.1)</t>
+          <t>-0.33** (-2.3)</t>
         </is>
       </c>
     </row>
@@ -913,34 +913,34 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.00** (-2.5)</t>
+          <t>-0.54*** (-2.8)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-0.00** (-2.5)</t>
+          <t>-0.51*** (-2.7)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-0.00** (-2.5)</t>
+          <t>-0.54*** (-2.8)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-0.00** (-2.5)</t>
+          <t>-0.53*** (-2.8)</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.00** (-2.5)</t>
+          <t>-0.54*** (-2.8)</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-0.00** (-2.6)</t>
+          <t>-0.55*** (-2.8)</t>
         </is>
       </c>
     </row>
@@ -953,34 +953,34 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.00*** (2.9)</t>
+          <t>0.31*** (2.6)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.00*** (2.8)</t>
+          <t>0.18 (1.4)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.00*** (2.9)</t>
+          <t>0.31*** (2.6)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.00*** (2.9)</t>
+          <t>0.29** (2.4)</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.00*** (2.9)</t>
+          <t>0.31*** (2.6)</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.00*** (3.0)</t>
+          <t>0.31*** (2.7)</t>
         </is>
       </c>
     </row>
@@ -1113,46 +1113,46 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0005108569398586662</v>
+        <v>3.853854232918517</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.0001098654574948997</v>
+        <v>1.011287241894017</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0004506853241422774</v>
+        <v>2.446774616065345</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>2.2598342208911e-05</v>
+        <v>0.1593852846071442</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0003615971451088711</v>
+        <v>1.852542399227079</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>1.38889065973894e-05</v>
+        <v>0.07453220317442487</v>
       </c>
       <c r="K2" t="n">
-        <v>3.334046646532902</v>
+        <v>6.834812349752647</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>2.381895256092411</v>
+        <v>2.378269714906367</v>
       </c>
       <c r="N2" t="n">
-        <v>3.528980044526917</v>
+        <v>5.077304916846577</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>0.9432680734704026</v>
+        <v>1.259523968718567</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.677682692093815</v>
+        <v>4.757403846245063</v>
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>0.6665965098898405</v>
+        <v>0.90783764888459</v>
       </c>
     </row>
     <row r="3">
@@ -1163,45 +1163,45 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>-0.0001878885059385489</v>
+        <v>-0.3402918698413656</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0001926625325590219</v>
+        <v>-0.345312297676962</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>-0.0001878885059385489</v>
+        <v>-0.3402918698413656</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.0001911218303361775</v>
+        <v>-0.341943388611391</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>-0.0001878885059385489</v>
+        <v>-0.3402918698413656</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.0001934861232838407</v>
+        <v>-0.3448471006347361</v>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>-2.384382854510064</v>
+        <v>-2.165122447801015</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.371853170274498</v>
+        <v>-2.18101878876803</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>-2.384382854510064</v>
+        <v>-2.165122447801015</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.372309131613424</v>
+        <v>-2.176814900841465</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>-2.384382854510064</v>
+        <v>-2.165122447801015</v>
       </c>
       <c r="S3" t="n">
-        <v>-2.40253605692536</v>
+        <v>-2.203653058191708</v>
       </c>
     </row>
     <row r="4">
@@ -1212,45 +1212,45 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>0.0003618509412752003</v>
+        <v>0.6714213031274484</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0003603185948978621</v>
+        <v>0.6663937125070409</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>0.0003618509412752003</v>
+        <v>0.6714213031274484</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0003528923772681047</v>
+        <v>0.6534294041098119</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>0.0003618509412752003</v>
+        <v>0.6714213031274484</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0003627573042619262</v>
+        <v>0.6685079528482804</v>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>2.973870035201673</v>
+        <v>3.754613724559088</v>
       </c>
       <c r="M4" t="n">
-        <v>2.884303569793766</v>
+        <v>3.69321911025523</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>2.973870035201673</v>
+        <v>3.754613724559088</v>
       </c>
       <c r="P4" t="n">
-        <v>2.883837374676061</v>
+        <v>3.672442344877934</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
-        <v>2.973870035201673</v>
+        <v>3.754613724559088</v>
       </c>
       <c r="S4" t="n">
-        <v>2.95474709886236</v>
+        <v>3.75247464564784</v>
       </c>
     </row>
     <row r="5">
@@ -1261,45 +1261,45 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>0.0005264363905298068</v>
+        <v>0.5021475456812518</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0004824228596891353</v>
+        <v>0.3242295994027844</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>0.0005264363905298068</v>
+        <v>0.5021475456812518</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0005276193247274772</v>
+        <v>0.4708264639117451</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>0.0005264363905298068</v>
+        <v>0.5021475456812518</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0005358228777935984</v>
+        <v>0.4956305312647842</v>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>2.818625024950651</v>
+        <v>2.682165307816009</v>
       </c>
       <c r="M5" t="n">
-        <v>2.682960833439439</v>
+        <v>1.676728025437014</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>2.818625024950651</v>
+        <v>2.682165307816009</v>
       </c>
       <c r="P5" t="n">
-        <v>2.813089312214194</v>
+        <v>2.48016515829088</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
-        <v>2.818625024950651</v>
+        <v>2.682165307816009</v>
       </c>
       <c r="S5" t="n">
-        <v>2.896313745942449</v>
+        <v>2.676771123091598</v>
       </c>
     </row>
     <row r="6">
@@ -1310,45 +1310,45 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>4.687090280262154e-05</v>
+        <v>0.07680342900671061</v>
       </c>
       <c r="D6" t="n">
-        <v>5.082085951801206e-05</v>
+        <v>0.06994217246962614</v>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>4.687090280262154e-05</v>
+        <v>0.07680342900671061</v>
       </c>
       <c r="G6" t="n">
-        <v>4.1624626454766e-05</v>
+        <v>0.06154322365887702</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>4.687090280262154e-05</v>
+        <v>0.07680342900671061</v>
       </c>
       <c r="J6" t="n">
-        <v>4.04598833234678e-05</v>
+        <v>0.0624807627673435</v>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>0.7567435515006108</v>
+        <v>0.6496400173897757</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8177801264709421</v>
+        <v>0.5992831606242297</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>0.7567435515006108</v>
+        <v>0.6496400173897757</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7051104918527875</v>
+        <v>0.5311477206451786</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
-        <v>0.7567435515006108</v>
+        <v>0.6496400173897757</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6492842182148379</v>
+        <v>0.5313043640284895</v>
       </c>
     </row>
     <row r="7">
@@ -1359,45 +1359,45 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>8.352695610996678e-05</v>
+        <v>0.1810109179997404</v>
       </c>
       <c r="D7" t="n">
-        <v>8.213317608642885e-05</v>
+        <v>0.1651224491396631</v>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>8.352695610996678e-05</v>
+        <v>0.1810109179997404</v>
       </c>
       <c r="G7" t="n">
-        <v>8.291676984522326e-05</v>
+        <v>0.1772832561516841</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>8.352695610996678e-05</v>
+        <v>0.1810109179997404</v>
       </c>
       <c r="J7" t="n">
-        <v>8.229714942382869e-05</v>
+        <v>0.1755327224011761</v>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>1.903649205508712</v>
+        <v>1.734698807887168</v>
       </c>
       <c r="M7" t="n">
-        <v>1.811324937808943</v>
+        <v>1.571533208765712</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
-        <v>1.903649205508712</v>
+        <v>1.734698807887168</v>
       </c>
       <c r="P7" t="n">
-        <v>1.853785956547742</v>
+        <v>1.679340616125107</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="n">
-        <v>1.903649205508712</v>
+        <v>1.734698807887168</v>
       </c>
       <c r="S7" t="n">
-        <v>1.903637346881646</v>
+        <v>1.702188426014724</v>
       </c>
     </row>
     <row r="8">
@@ -1408,45 +1408,45 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>-0.0001552301798038173</v>
+        <v>-0.3337900761475555</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0001569500735747802</v>
+        <v>-0.3374501897199102</v>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>-0.0001552301798038173</v>
+        <v>-0.3337900761475555</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0001501089133090205</v>
+        <v>-0.3310186667525482</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>-0.0001552301798038173</v>
+        <v>-0.3337900761475555</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.0001518166755035399</v>
+        <v>-0.3273551928738235</v>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>-3.107710990373483</v>
+        <v>-3.257228115068398</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.130521478046632</v>
+        <v>-3.339421585818187</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
-        <v>-3.107710990373483</v>
+        <v>-3.257228115068398</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.918204908471754</v>
+        <v>-3.172311819761468</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="n">
-        <v>-3.107710990373483</v>
+        <v>-3.257228115068398</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.945638211216679</v>
+        <v>-3.15699140802385</v>
       </c>
     </row>
     <row r="9">
@@ -1457,45 +1457,45 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>-6.867638807073069e-05</v>
+        <v>-0.1171732193627874</v>
       </c>
       <c r="D9" t="n">
-        <v>-6.516866082003595e-05</v>
+        <v>-0.1174347188188426</v>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>-6.867638807073069e-05</v>
+        <v>-0.1171732193627874</v>
       </c>
       <c r="G9" t="n">
-        <v>-6.652889610034604e-05</v>
+        <v>-0.1182338974049036</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>-6.867638807073069e-05</v>
+        <v>-0.1171732193627874</v>
       </c>
       <c r="J9" t="n">
-        <v>-7.050855036114736e-05</v>
+        <v>-0.1196039337490956</v>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>-1.214170844447103</v>
+        <v>-1.217709652782119</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.2319747081146</v>
+        <v>-1.294046309668714</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="n">
-        <v>-1.214170844447103</v>
+        <v>-1.217709652782119</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.220781275858213</v>
+        <v>-1.245359992672164</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="n">
-        <v>-1.214170844447103</v>
+        <v>-1.217709652782119</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.240910832099047</v>
+        <v>-1.251578532309869</v>
       </c>
     </row>
     <row r="10">
@@ -1506,45 +1506,45 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>-0.0004516982583716013</v>
+        <v>-0.8742849579323837</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0004568261320594474</v>
+        <v>-0.8595373065266426</v>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>-0.0004516982583716013</v>
+        <v>-0.8742849579323837</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0004615638844346764</v>
+        <v>-0.8755651975407722</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>-0.0004516982583716013</v>
+        <v>-0.8742849579323837</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.0004645177219753559</v>
+        <v>-0.8883170583612308</v>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>-3.821017259713714</v>
+        <v>-4.01957883712022</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.725586294528477</v>
+        <v>-3.921887312581746</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>-3.821017259713714</v>
+        <v>-4.01957883712022</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.760676914544739</v>
+        <v>-3.97771505634085</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="n">
-        <v>-3.821017259713714</v>
+        <v>-4.01957883712022</v>
       </c>
       <c r="S10" t="n">
-        <v>-3.800099296877871</v>
+        <v>-4.01317364503115</v>
       </c>
     </row>
     <row r="11">
@@ -1555,45 +1555,45 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>0.0004750136611938317</v>
+        <v>0.4048972051582778</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0004430204321771272</v>
+        <v>0.2497088721706784</v>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>0.0004750136611938317</v>
+        <v>0.4048972051582778</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0004768335925981045</v>
+        <v>0.3811478716217246</v>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>0.0004750136611938317</v>
+        <v>0.4048972051582778</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0004834262420573671</v>
+        <v>0.4006750329795756</v>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>2.875390766168186</v>
+        <v>2.798860388854958</v>
       </c>
       <c r="M11" t="n">
-        <v>2.780285999973748</v>
+        <v>1.64694288374359</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="n">
-        <v>2.875390766168186</v>
+        <v>2.798860388854958</v>
       </c>
       <c r="P11" t="n">
-        <v>2.874900562714452</v>
+        <v>2.551281483305581</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="n">
-        <v>2.875390766168186</v>
+        <v>2.798860388854958</v>
       </c>
       <c r="S11" t="n">
-        <v>2.958501262772149</v>
+        <v>2.812537626793815</v>
       </c>
     </row>
     <row r="12">
@@ -1604,45 +1604,45 @@
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
-        <v>-0.0001482734633297038</v>
+        <v>-0.331636225632104</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.0001489904811248019</v>
+        <v>-0.342689420906735</v>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
-        <v>-0.0001482734633297038</v>
+        <v>-0.331636225632104</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.0001420854982651478</v>
+        <v>-0.3233809136527854</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>-0.0001482734633297038</v>
+        <v>-0.331636225632104</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.0001456958309245595</v>
+        <v>-0.3320348039398012</v>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>-2.135067002022432</v>
+        <v>-2.285761853037302</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.131208575439137</v>
+        <v>-2.402306118431336</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
-        <v>-2.135067002022432</v>
+        <v>-2.285761853037302</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.011000086105933</v>
+        <v>-2.236735509865702</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="n">
-        <v>-2.135067002022432</v>
+        <v>-2.285761853037302</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.064043133051634</v>
+        <v>-2.307151623804646</v>
       </c>
     </row>
     <row r="13">
@@ -1653,45 +1653,45 @@
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>-0.0002714565076879463</v>
+        <v>-0.5351765347525901</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0002666459479327336</v>
+        <v>-0.5107171406277659</v>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>-0.0002714565076879463</v>
+        <v>-0.5351765347525901</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0002763778922928192</v>
+        <v>-0.5326872363745229</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>-0.0002714565076879463</v>
+        <v>-0.5351765347525901</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.0002804758558574621</v>
+        <v>-0.5485036545173941</v>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>-2.548871090387237</v>
+        <v>-2.802316220405125</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.491670974351206</v>
+        <v>-2.683056542376665</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="n">
-        <v>-2.548871090387237</v>
+        <v>-2.802316220405125</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.539645779259414</v>
+        <v>-2.783815219940543</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="n">
-        <v>-2.548871090387237</v>
+        <v>-2.802316220405125</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.562068281728417</v>
+        <v>-2.818017131875585</v>
       </c>
     </row>
     <row r="14">
@@ -1702,45 +1702,45 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>0.0004235909318578453</v>
+        <v>0.307646864635311</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0004036180046651059</v>
+        <v>0.1751881449385752</v>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
-        <v>0.0004235909318578453</v>
+        <v>0.307646864635311</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0004260478604687274</v>
+        <v>0.2914692793317035</v>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>0.0004235909318578453</v>
+        <v>0.307646864635311</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0004310296063211295</v>
+        <v>0.3057195346943682</v>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
-        <v>2.890346132352859</v>
+        <v>2.634842963046265</v>
       </c>
       <c r="M14" t="n">
-        <v>2.846595065127501</v>
+        <v>1.430382979269115</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="n">
-        <v>2.890346132352859</v>
+        <v>2.634842963046265</v>
       </c>
       <c r="P14" t="n">
-        <v>2.898691241009096</v>
+        <v>2.362462081522872</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="n">
-        <v>2.890346132352859</v>
+        <v>2.634842963046265</v>
       </c>
       <c r="S14" t="n">
-        <v>2.979088631304117</v>
+        <v>2.676331594715097</v>
       </c>
     </row>
     <row r="15">

--- a/outputs/05_benchmark_signals/tables_v_viii/cn/table_vii_return_logit.xlsx
+++ b/outputs/05_benchmark_signals/tables_v_viii/cn/table_vii_return_logit.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="display" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="raw" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="display_stars" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="raw" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1011,6 +1012,603 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>I5_R5_CNN</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>I5_R5_Chars</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>I5_R5_Joint</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>I20_R5_CNN</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>I20_R5_Chars</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>I20_R5_Joint</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>I60_R5_CNN</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>I60_R5_Chars</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>I60_R5_Joint</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CNN</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>3.85***</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1.01**</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2.45***</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.16</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>1.85***</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>MOM</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>-0.34**</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>-0.35**</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>-0.34**</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-0.34**</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-0.34**</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-0.34**</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>STR</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0.67***</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0.67***</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0.67***</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.65***</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.67***</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0.67***</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>WSTR</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0.50***</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0.32*</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0.50***</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.47**</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.50***</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0.50***</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TREND</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0.18*</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0.17</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0.18*</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0.18*</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.18*</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.18*</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Volat.</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>-0.33***</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>-0.34***</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>-0.33***</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-0.33***</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>-0.33***</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-0.33***</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>52WH</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Dollar Volume</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>-0.87***</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>-0.86***</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>-0.87***</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-0.88***</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>-0.87***</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>-0.89***</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Zero Trade</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0.40***</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>0.25*</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0.40***</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0.38**</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0.40***</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0.40***</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Size</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>-0.33**</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>-0.34**</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>-0.33**</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-0.32**</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-0.33**</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>-0.33**</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Illiq.</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>-0.54***</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>-0.51***</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-0.54***</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-0.53***</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>-0.54***</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>-0.55***</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Lag Weekly Return</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0.31***</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0.18</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0.31***</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0.29**</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0.31***</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0.31***</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>OOS McFadden R²</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:S15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/outputs/05_benchmark_signals/tables_v_viii/cn/table_vii_return_logit.xlsx
+++ b/outputs/05_benchmark_signals/tables_v_viii/cn/table_vii_return_logit.xlsx
@@ -473,7 +473,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3.85*** (6.8)</t>
+          <t>1.60*** (3.0)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
@@ -484,7 +484,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2.45*** (5.1)</t>
+          <t>0.77*** (3.7)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -495,7 +495,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1.85*** (4.8)</t>
+          <t>0.48*** (3.5)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3.85***</t>
+          <t>1.60***</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2.45***</t>
+          <t>0.77***</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1.85***</t>
+          <t>0.48***</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -1711,42 +1711,42 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.853854232918517</v>
+        <v>1.596704469189518</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
         <v>1.011287241894017</v>
       </c>
       <c r="E2" t="n">
-        <v>2.446774616065345</v>
+        <v>0.773573037475353</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
         <v>0.1593852846071442</v>
       </c>
       <c r="H2" t="n">
-        <v>1.852542399227079</v>
+        <v>0.4833046761211478</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
         <v>0.07453220317442487</v>
       </c>
       <c r="K2" t="n">
-        <v>6.834812349752647</v>
+        <v>3.02526678272412</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>2.378269714906367</v>
       </c>
       <c r="N2" t="n">
-        <v>5.077304916846577</v>
+        <v>3.745987916569298</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
         <v>1.259523968718567</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.757403846245063</v>
+        <v>3.497027205059362</v>
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
